--- a/data/raw/sales/Week 16/Audio_Array/other_channels.xlsx
+++ b/data/raw/sales/Week 16/Audio_Array/other_channels.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\sales\Week 16\Audio_Array\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B485DF-0D7D-4071-BCF6-7A5E8C5C9C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25BE3A89-6A72-42A8-A6BC-E3EF709E395C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CRED_B2C" sheetId="4" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="400">
   <si>
     <t>SKU</t>
   </si>
@@ -1135,9 +1135,6 @@
   </si>
   <si>
     <t>B0G2C2RCXN</t>
-  </si>
-  <si>
-    <t>AI-04</t>
   </si>
   <si>
     <t>Enertia</t>
@@ -1253,7 +1250,7 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;₹&quot;\ #,##0.00;[Red]&quot;₹&quot;\ \-#,##0.00"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1291,12 +1288,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
@@ -1423,7 +1414,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1465,70 +1456,61 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2155,7 +2137,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:X923"/>
+  <dimension ref="A1:X915"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.109375" customWidth="1"/>
@@ -2206,162 +2188,162 @@
       <c r="X1" s="4"/>
     </row>
     <row r="2" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
-        <v>362</v>
-      </c>
-      <c r="B2" s="16" t="s">
+      <c r="A2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="17">
+      <c r="E2">
         <v>2</v>
       </c>
-      <c r="F2" s="18">
-        <v>8642.3700000000008</v>
+      <c r="F2">
+        <v>8642</v>
       </c>
     </row>
     <row r="3" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="15" t="s">
-        <v>362</v>
-      </c>
-      <c r="B3" s="16" t="s">
+      <c r="A3" t="s">
+        <v>362</v>
+      </c>
+      <c r="B3" t="s">
         <v>152</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" t="s">
         <v>154</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" t="s">
         <v>153</v>
       </c>
-      <c r="E3" s="17">
-        <v>21</v>
-      </c>
-      <c r="F3" s="18">
-        <v>33795.760000000002</v>
+      <c r="E3">
+        <v>26</v>
+      </c>
+      <c r="F3">
+        <v>47224</v>
       </c>
     </row>
     <row r="4" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
-        <v>362</v>
-      </c>
-      <c r="B4" s="16" t="s">
+      <c r="A4" t="s">
+        <v>362</v>
+      </c>
+      <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="17">
-        <v>5</v>
-      </c>
-      <c r="F4" s="18">
-        <v>11266.95</v>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>9149</v>
       </c>
     </row>
     <row r="5" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
-        <v>362</v>
-      </c>
-      <c r="B5" s="16" t="s">
+      <c r="A5" t="s">
+        <v>362</v>
+      </c>
+      <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="16" t="s">
-        <v>365</v>
-      </c>
-      <c r="E5" s="17">
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5" s="18">
-        <v>4066.95</v>
+      <c r="F5">
+        <v>4067</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
-        <v>362</v>
-      </c>
-      <c r="B6" s="16" t="s">
+      <c r="A6" t="s">
+        <v>362</v>
+      </c>
+      <c r="B6" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="17">
-        <v>4</v>
-      </c>
-      <c r="F6" s="18">
-        <v>11925.42</v>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>2981</v>
       </c>
     </row>
     <row r="7" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
-        <v>362</v>
-      </c>
-      <c r="B7" s="16" t="s">
+      <c r="A7" t="s">
+        <v>362</v>
+      </c>
+      <c r="B7" t="s">
         <v>238</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" t="s">
         <v>240</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" t="s">
         <v>239</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7">
         <v>3</v>
       </c>
-      <c r="F7" s="18">
-        <v>4022.88</v>
+      <c r="F7">
+        <v>4828</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
-        <v>362</v>
-      </c>
-      <c r="B8" s="16" t="s">
+      <c r="A8" t="s">
+        <v>362</v>
+      </c>
+      <c r="B8" t="s">
         <v>89</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" t="s">
         <v>91</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" t="s">
         <v>90</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F8">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="15" t="s">
-        <v>362</v>
-      </c>
-      <c r="B9" s="16" t="s">
+      <c r="A9" t="s">
+        <v>362</v>
+      </c>
+      <c r="B9" t="s">
         <v>224</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" t="s">
         <v>226</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" t="s">
         <v>225</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F9">
         <v>0</v>
       </c>
     </row>
@@ -3271,14 +3253,6 @@
     <row r="913" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="914" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="915" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="916" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="917" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="918" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="919" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="920" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="921" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="922" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="923" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -5735,1337 +5709,1337 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="16">
         <v>1</v>
       </c>
-      <c r="E2" s="19">
+      <c r="E2" s="16">
         <v>1907</v>
       </c>
-      <c r="F2" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G2" s="20" t="s">
+      <c r="F2" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="D3" s="16">
+        <v>2</v>
+      </c>
+      <c r="E3" s="16">
+        <v>2032</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="16">
+        <v>20</v>
+      </c>
+      <c r="E4" s="16">
+        <v>19667.8</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G4" s="17" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="19" t="s">
-        <v>224</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>226</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>225</v>
-      </c>
-      <c r="D3" s="19">
+    <row r="5" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="16">
+        <v>1</v>
+      </c>
+      <c r="E5" s="16">
+        <v>2987</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="16">
         <v>2</v>
       </c>
-      <c r="E3" s="19">
-        <v>2032</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G3" s="20" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" s="19">
-        <v>20</v>
-      </c>
-      <c r="E4" s="19">
-        <v>19667.8</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G4" s="20" t="s">
+      <c r="E6" s="16">
+        <v>6228</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G6" s="17" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D5" s="19">
-        <v>1</v>
-      </c>
-      <c r="E5" s="19">
-        <v>2987</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G5" s="20" t="s">
+    <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="D7" s="16">
+        <v>2</v>
+      </c>
+      <c r="E7" s="16">
+        <v>4640</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="16">
+        <v>2</v>
+      </c>
+      <c r="E8" s="16">
+        <v>2034</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="16">
+        <v>30</v>
+      </c>
+      <c r="E9" s="16">
+        <v>115142</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G9" s="17" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="19">
-        <v>2</v>
-      </c>
-      <c r="E6" s="19">
-        <v>6228</v>
-      </c>
-      <c r="F6" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>255</v>
-      </c>
-      <c r="C7" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="D7" s="19">
-        <v>2</v>
-      </c>
-      <c r="E7" s="19">
-        <v>4640</v>
-      </c>
-      <c r="F7" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G7" s="20" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="C8" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8" s="19">
-        <v>2</v>
-      </c>
-      <c r="E8" s="19">
-        <v>2034</v>
-      </c>
-      <c r="F8" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="19">
-        <v>30</v>
-      </c>
-      <c r="E9" s="19">
-        <v>115142</v>
-      </c>
-      <c r="F9" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G9" s="20" t="s">
-        <v>369</v>
-      </c>
-    </row>
     <row r="10" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="17" t="s">
         <v>31</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="16">
         <v>35</v>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="16">
         <v>53795</v>
       </c>
-      <c r="F10" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G10" s="20" t="s">
-        <v>370</v>
+      <c r="F10" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="17" t="s">
         <v>31</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="16">
         <v>35</v>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="16">
         <v>53795</v>
       </c>
-      <c r="F11" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G11" s="20" t="s">
+      <c r="F11" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="22">
+        <v>2</v>
+      </c>
+      <c r="E12" s="23">
+        <v>4186.4399999999996</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G12" s="17" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="25">
+    <row r="13" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="D13" s="15">
         <v>2</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E13" s="23">
+        <v>2423.73</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="D14" s="15">
+        <v>2</v>
+      </c>
+      <c r="E14" s="23">
+        <v>6610.17</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="D15" s="15">
+        <v>4</v>
+      </c>
+      <c r="E15" s="23">
+        <v>1101.69</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G15" s="17" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="D16" s="15">
+        <v>6</v>
+      </c>
+      <c r="E16" s="23">
+        <v>4296.6099999999997</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G16" s="17" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="15">
+        <v>2</v>
+      </c>
+      <c r="E17" s="23">
+        <v>1762.71</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G17" s="17" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="15">
+        <v>10</v>
+      </c>
+      <c r="E18" s="23">
+        <v>26991.53</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G18" s="17" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="21" t="s">
+        <v>253</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D19" s="15">
+        <v>3</v>
+      </c>
+      <c r="E19" s="23">
+        <v>6031.78</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G19" s="17" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="15">
+        <v>1</v>
+      </c>
+      <c r="E20" s="23">
+        <v>2148.31</v>
+      </c>
+      <c r="F20" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="21" t="s">
+        <v>371</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>372</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>373</v>
+      </c>
+      <c r="D21" s="15">
+        <v>6</v>
+      </c>
+      <c r="E21" s="23">
+        <v>6940.68</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G21" s="17" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="D22" s="15">
+        <v>3</v>
+      </c>
+      <c r="E22" s="23">
+        <v>2809.32</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G22" s="17" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" s="15">
+        <v>2</v>
+      </c>
+      <c r="E23" s="23">
+        <v>1762.71</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G23" s="17" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D24" s="15">
+        <v>10</v>
+      </c>
+      <c r="E24" s="23">
+        <v>25889.83</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="D25" s="15">
+        <v>8</v>
+      </c>
+      <c r="E25" s="23">
+        <v>7491.53</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G25" s="17" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>375</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>376</v>
+      </c>
+      <c r="D26" s="15">
+        <v>6</v>
+      </c>
+      <c r="E26" s="23">
+        <v>10169.49</v>
+      </c>
+      <c r="F26" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G26" s="17" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="D27" s="15">
+        <v>4</v>
+      </c>
+      <c r="E27" s="23">
+        <v>8372.8799999999992</v>
+      </c>
+      <c r="F27" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G27" s="17" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="D28" s="15">
+        <v>4</v>
+      </c>
+      <c r="E28" s="23">
+        <v>13881.36</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G28" s="17" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="15">
+        <v>4</v>
+      </c>
+      <c r="E29" s="23">
+        <v>19830.509999999998</v>
+      </c>
+      <c r="F29" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G29" s="17" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="D30" s="15">
+        <v>10</v>
+      </c>
+      <c r="E30" s="23">
+        <v>19555.080000000002</v>
+      </c>
+      <c r="F30" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G30" s="17" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>377</v>
+      </c>
+      <c r="D31" s="15">
+        <v>2</v>
+      </c>
+      <c r="E31" s="23">
+        <v>2203.39</v>
+      </c>
+      <c r="F31" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G31" s="17" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D32" s="15">
+        <v>2</v>
+      </c>
+      <c r="E32" s="23">
+        <v>2203.39</v>
+      </c>
+      <c r="F32" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G32" s="17" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="21" t="s">
+        <v>378</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>379</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>380</v>
+      </c>
+      <c r="D33" s="15">
+        <v>2</v>
+      </c>
+      <c r="E33" s="23">
+        <v>9364.41</v>
+      </c>
+      <c r="F33" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G33" s="17" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="D34" s="15">
+        <v>4</v>
+      </c>
+      <c r="E34" s="23">
         <v>4186.4399999999996</v>
       </c>
-      <c r="F12" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G12" s="20" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="24" t="s">
-        <v>229</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>231</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>230</v>
-      </c>
-      <c r="D13" s="17">
+      <c r="F34" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G34" s="17" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="21" t="s">
+        <v>381</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>382</v>
+      </c>
+      <c r="C35" s="34" t="s">
+        <v>398</v>
+      </c>
+      <c r="D35" s="15">
+        <v>4</v>
+      </c>
+      <c r="E35" s="23">
+        <v>1872.88</v>
+      </c>
+      <c r="F35" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G35" s="17" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="D36" s="15">
+        <v>3</v>
+      </c>
+      <c r="E36" s="23">
+        <v>907.25</v>
+      </c>
+      <c r="F36" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G36" s="17" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="D37" s="15">
         <v>2</v>
       </c>
-      <c r="E13" s="26">
-        <v>2423.73</v>
-      </c>
-      <c r="F13" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G13" s="20" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="D14" s="17">
+      <c r="E37" s="23">
+        <v>2753.14</v>
+      </c>
+      <c r="F37" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G37" s="17" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="21" t="s">
+        <v>383</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>384</v>
+      </c>
+      <c r="C38" s="34" t="s">
+        <v>399</v>
+      </c>
+      <c r="D38" s="15">
+        <v>1</v>
+      </c>
+      <c r="E38" s="23">
+        <v>11652.54</v>
+      </c>
+      <c r="F38" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G38" s="16" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C39" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="D39" s="24">
+        <v>40</v>
+      </c>
+      <c r="E39" s="24">
+        <v>19600</v>
+      </c>
+      <c r="F39" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G39" s="16" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="24" t="s">
+        <v>221</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="C40" s="25" t="s">
+        <v>222</v>
+      </c>
+      <c r="D40" s="24">
+        <v>12</v>
+      </c>
+      <c r="E40" s="24">
+        <v>10920</v>
+      </c>
+      <c r="F40" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G40" s="16" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C41" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="D41" s="24">
+        <v>21</v>
+      </c>
+      <c r="E41" s="24">
+        <v>55125</v>
+      </c>
+      <c r="F41" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G41" s="16" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="B42" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C42" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="D42" s="24">
+        <v>10</v>
+      </c>
+      <c r="E42" s="24">
+        <v>21700</v>
+      </c>
+      <c r="F42" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G42" s="16" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="C43" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="D43" s="24">
+        <v>32</v>
+      </c>
+      <c r="E43" s="24">
+        <v>31360</v>
+      </c>
+      <c r="F43" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G43" s="16" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C44" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="D44" s="24">
+        <v>48</v>
+      </c>
+      <c r="E44" s="26">
+        <v>53760</v>
+      </c>
+      <c r="F44" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G44" s="16" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="24" t="s">
+        <v>378</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>379</v>
+      </c>
+      <c r="C45" s="25" t="s">
+        <v>380</v>
+      </c>
+      <c r="D45" s="24">
+        <v>10</v>
+      </c>
+      <c r="E45" s="26">
+        <v>59500</v>
+      </c>
+      <c r="F45" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G45" s="16" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="24" t="s">
+        <v>386</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>387</v>
+      </c>
+      <c r="C46" s="25" t="s">
+        <v>388</v>
+      </c>
+      <c r="D46" s="24">
+        <v>10</v>
+      </c>
+      <c r="E46" s="26">
+        <v>77000</v>
+      </c>
+      <c r="F46" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G46" s="16" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>389</v>
+      </c>
+      <c r="C47" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="D47" s="24">
+        <v>3</v>
+      </c>
+      <c r="E47" s="26">
+        <v>4131.3599999999997</v>
+      </c>
+      <c r="F47" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G47" s="17" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="B48" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="C48" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="D48" s="24">
+        <v>6</v>
+      </c>
+      <c r="E48" s="26">
+        <v>6279.66</v>
+      </c>
+      <c r="F48" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G48" s="17" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="24" t="s">
+        <v>390</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="C49" s="27" t="s">
+        <v>225</v>
+      </c>
+      <c r="D49" s="28">
+        <v>4</v>
+      </c>
+      <c r="E49" s="29">
+        <v>4745.76</v>
+      </c>
+      <c r="F49" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G49" s="16" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C50" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="D50" s="27">
         <v>2</v>
       </c>
-      <c r="E14" s="26">
-        <v>6610.17</v>
-      </c>
-      <c r="F14" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G14" s="20" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>220</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>219</v>
-      </c>
-      <c r="D15" s="17">
+      <c r="E50" s="30">
+        <v>1898.31</v>
+      </c>
+      <c r="F50" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G50" s="16" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="24" t="s">
+        <v>235</v>
+      </c>
+      <c r="B51" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="C51" s="27" t="s">
+        <v>393</v>
+      </c>
+      <c r="D51" s="27">
+        <v>2</v>
+      </c>
+      <c r="E51" s="30">
+        <v>2372.88</v>
+      </c>
+      <c r="F51" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G51" s="16" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="B52" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="C52" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="D52" s="27">
+        <v>2</v>
+      </c>
+      <c r="E52" s="30">
+        <v>2372.88</v>
+      </c>
+      <c r="F52" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G52" s="16" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C53" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="D53" s="27">
         <v>4</v>
       </c>
-      <c r="E15" s="26">
-        <v>1101.69</v>
-      </c>
-      <c r="F15" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G15" s="20" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="24" t="s">
-        <v>221</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>223</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>222</v>
-      </c>
-      <c r="D16" s="17">
-        <v>6</v>
-      </c>
-      <c r="E16" s="26">
-        <v>4296.6099999999997</v>
-      </c>
-      <c r="F16" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G16" s="20" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" s="17">
+      <c r="E53" s="30">
+        <v>4745.76</v>
+      </c>
+      <c r="F53" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G53" s="16" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="24" t="s">
+        <v>386</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>387</v>
+      </c>
+      <c r="C54" s="27" t="s">
+        <v>388</v>
+      </c>
+      <c r="D54" s="27">
         <v>2</v>
       </c>
-      <c r="E17" s="26">
-        <v>1762.71</v>
-      </c>
-      <c r="F17" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G17" s="20" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="17">
-        <v>10</v>
-      </c>
-      <c r="E18" s="26">
-        <v>26991.53</v>
-      </c>
-      <c r="F18" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G18" s="20" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="24" t="s">
-        <v>253</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>255</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>254</v>
-      </c>
-      <c r="D19" s="17">
-        <v>3</v>
-      </c>
-      <c r="E19" s="26">
-        <v>6031.78</v>
-      </c>
-      <c r="F19" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G19" s="20" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="B20" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="D20" s="17">
-        <v>1</v>
-      </c>
-      <c r="E20" s="26">
-        <v>2148.31</v>
-      </c>
-      <c r="F20" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G20" s="20" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="24" t="s">
-        <v>372</v>
-      </c>
-      <c r="B21" s="20" t="s">
-        <v>373</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>374</v>
-      </c>
-      <c r="D21" s="17">
-        <v>6</v>
-      </c>
-      <c r="E21" s="26">
-        <v>6940.68</v>
-      </c>
-      <c r="F21" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G21" s="20" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="B22" s="20" t="s">
-        <v>211</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>210</v>
-      </c>
-      <c r="D22" s="17">
-        <v>3</v>
-      </c>
-      <c r="E22" s="26">
-        <v>2809.32</v>
-      </c>
-      <c r="F22" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G22" s="20" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="B23" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="D23" s="17">
+      <c r="E54" s="30">
+        <v>13050.85</v>
+      </c>
+      <c r="F54" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G54" s="16" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="24" t="s">
+        <v>394</v>
+      </c>
+      <c r="B55" s="16" t="s">
+        <v>395</v>
+      </c>
+      <c r="C55" s="27" t="s">
+        <v>396</v>
+      </c>
+      <c r="D55" s="27">
         <v>2</v>
       </c>
-      <c r="E23" s="26">
-        <v>1762.71</v>
-      </c>
-      <c r="F23" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G23" s="20" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="B24" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="D24" s="17">
-        <v>10</v>
-      </c>
-      <c r="E24" s="26">
-        <v>25889.83</v>
-      </c>
-      <c r="F24" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G24" s="20" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="24" t="s">
-        <v>152</v>
-      </c>
-      <c r="B25" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="D25" s="17">
-        <v>8</v>
-      </c>
-      <c r="E25" s="26">
-        <v>7491.53</v>
-      </c>
-      <c r="F25" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G25" s="20" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="24" t="s">
-        <v>375</v>
-      </c>
-      <c r="B26" s="20" t="s">
-        <v>376</v>
-      </c>
-      <c r="C26" s="17" t="s">
-        <v>377</v>
-      </c>
-      <c r="D26" s="17">
-        <v>6</v>
-      </c>
-      <c r="E26" s="26">
-        <v>10169.49</v>
-      </c>
-      <c r="F26" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G26" s="20" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="24" t="s">
-        <v>203</v>
-      </c>
-      <c r="B27" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="C27" s="17" t="s">
-        <v>204</v>
-      </c>
-      <c r="D27" s="17">
-        <v>4</v>
-      </c>
-      <c r="E27" s="26">
-        <v>8372.8799999999992</v>
-      </c>
-      <c r="F27" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G27" s="20" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="B28" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="C28" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="D28" s="17">
-        <v>4</v>
-      </c>
-      <c r="E28" s="26">
-        <v>13881.36</v>
-      </c>
-      <c r="F28" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G28" s="20" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="B29" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="D29" s="17">
-        <v>4</v>
-      </c>
-      <c r="E29" s="26">
-        <v>19830.509999999998</v>
-      </c>
-      <c r="F29" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G29" s="20" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="B30" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="C30" s="17" t="s">
-        <v>165</v>
-      </c>
-      <c r="D30" s="17">
-        <v>10</v>
-      </c>
-      <c r="E30" s="26">
-        <v>19555.080000000002</v>
-      </c>
-      <c r="F30" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G30" s="20" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="B31" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="C31" s="17" t="s">
-        <v>378</v>
-      </c>
-      <c r="D31" s="17">
+      <c r="E55" s="30">
+        <v>4745.76</v>
+      </c>
+      <c r="F55" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G55" s="16" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="24" t="s">
+        <v>200</v>
+      </c>
+      <c r="B56" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="C56" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="D56" s="27">
         <v>2</v>
       </c>
-      <c r="E31" s="26">
-        <v>2203.39</v>
-      </c>
-      <c r="F31" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G31" s="20" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="B32" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="C32" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D32" s="17">
+      <c r="E56" s="30">
+        <v>4745.76</v>
+      </c>
+      <c r="F56" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G56" s="16" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="B57" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="C57" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="D57" s="27">
         <v>2</v>
       </c>
-      <c r="E32" s="26">
-        <v>2203.39</v>
-      </c>
-      <c r="F32" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G32" s="20" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="24" t="s">
-        <v>379</v>
-      </c>
-      <c r="B33" s="19" t="s">
-        <v>380</v>
-      </c>
-      <c r="C33" s="17" t="s">
-        <v>381</v>
-      </c>
-      <c r="D33" s="17">
+      <c r="E57" s="30">
+        <v>5932.2</v>
+      </c>
+      <c r="F57" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G57" s="16" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="B58" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="C58" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="D58" s="27">
         <v>2</v>
       </c>
-      <c r="E33" s="26">
-        <v>9364.41</v>
-      </c>
-      <c r="F33" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G33" s="20" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="24" t="s">
-        <v>182</v>
-      </c>
-      <c r="B34" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="C34" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="D34" s="17">
-        <v>4</v>
-      </c>
-      <c r="E34" s="26">
-        <v>4186.4399999999996</v>
-      </c>
-      <c r="F34" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G34" s="20" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="24" t="s">
-        <v>382</v>
-      </c>
-      <c r="B35" s="19" t="s">
+      <c r="E58" s="30">
+        <v>6525.42</v>
+      </c>
+      <c r="F58" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G58" s="16" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="32" t="s">
         <v>383</v>
       </c>
-      <c r="C35" s="37" t="s">
+      <c r="B59" s="31" t="s">
+        <v>384</v>
+      </c>
+      <c r="C59" s="34" t="s">
         <v>399</v>
       </c>
-      <c r="D35" s="17">
-        <v>4</v>
-      </c>
-      <c r="E35" s="26">
-        <v>1872.88</v>
-      </c>
-      <c r="F35" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G35" s="20" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="B36" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="C36" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="D36" s="17">
-        <v>3</v>
-      </c>
-      <c r="E36" s="26">
-        <v>907.25</v>
-      </c>
-      <c r="F36" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G36" s="20" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="B37" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="C37" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="D37" s="17">
+      <c r="D59" s="32">
         <v>2</v>
       </c>
-      <c r="E37" s="26">
-        <v>2753.14</v>
-      </c>
-      <c r="F37" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G37" s="20" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="24" t="s">
-        <v>384</v>
-      </c>
-      <c r="B38" s="19" t="s">
-        <v>385</v>
-      </c>
-      <c r="C38" s="37" t="s">
-        <v>400</v>
-      </c>
-      <c r="D38" s="17">
-        <v>1</v>
-      </c>
-      <c r="E38" s="26">
-        <v>11652.54</v>
-      </c>
-      <c r="F38" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G38" s="19" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="27" t="s">
-        <v>68</v>
-      </c>
-      <c r="B39" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="C39" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="D39" s="27">
-        <v>40</v>
-      </c>
-      <c r="E39" s="27">
-        <v>19600</v>
-      </c>
-      <c r="F39" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G39" s="19" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="27" t="s">
-        <v>221</v>
-      </c>
-      <c r="B40" s="19" t="s">
-        <v>223</v>
-      </c>
-      <c r="C40" s="28" t="s">
-        <v>222</v>
-      </c>
-      <c r="D40" s="27">
-        <v>12</v>
-      </c>
-      <c r="E40" s="27">
-        <v>10920</v>
-      </c>
-      <c r="F40" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G40" s="19" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="B41" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C41" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="D41" s="27">
-        <v>21</v>
-      </c>
-      <c r="E41" s="27">
-        <v>55125</v>
-      </c>
-      <c r="F41" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G41" s="19" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="B42" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="C42" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="D42" s="27">
-        <v>10</v>
-      </c>
-      <c r="E42" s="27">
-        <v>21700</v>
-      </c>
-      <c r="F42" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G42" s="19" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="B43" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C43" s="37" t="s">
-        <v>54</v>
-      </c>
-      <c r="D43" s="27">
-        <v>32</v>
-      </c>
-      <c r="E43" s="27">
-        <v>31360</v>
-      </c>
-      <c r="F43" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G43" s="19" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="27" t="s">
-        <v>59</v>
-      </c>
-      <c r="B44" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C44" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="D44" s="27">
-        <v>48</v>
-      </c>
-      <c r="E44" s="29">
-        <v>53760</v>
-      </c>
-      <c r="F44" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G44" s="19" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="27" t="s">
-        <v>379</v>
-      </c>
-      <c r="B45" s="19" t="s">
-        <v>380</v>
-      </c>
-      <c r="C45" s="28" t="s">
-        <v>381</v>
-      </c>
-      <c r="D45" s="27">
-        <v>10</v>
-      </c>
-      <c r="E45" s="29">
-        <v>59500</v>
-      </c>
-      <c r="F45" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G45" s="19" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="27" t="s">
-        <v>387</v>
-      </c>
-      <c r="B46" s="19" t="s">
-        <v>388</v>
-      </c>
-      <c r="C46" s="28" t="s">
-        <v>389</v>
-      </c>
-      <c r="D46" s="27">
-        <v>10</v>
-      </c>
-      <c r="E46" s="29">
-        <v>77000</v>
-      </c>
-      <c r="F46" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G46" s="19" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="B47" s="19" t="s">
-        <v>390</v>
-      </c>
-      <c r="C47" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="D47" s="27">
-        <v>3</v>
-      </c>
-      <c r="E47" s="29">
-        <v>4131.3599999999997</v>
-      </c>
-      <c r="F47" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G47" s="20" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="27" t="s">
-        <v>188</v>
-      </c>
-      <c r="B48" s="19" t="s">
-        <v>190</v>
-      </c>
-      <c r="C48" s="27" t="s">
-        <v>189</v>
-      </c>
-      <c r="D48" s="27">
-        <v>6</v>
-      </c>
-      <c r="E48" s="29">
-        <v>6279.66</v>
-      </c>
-      <c r="F48" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G48" s="20" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="27" t="s">
-        <v>391</v>
-      </c>
-      <c r="B49" s="19" t="s">
-        <v>392</v>
-      </c>
-      <c r="C49" s="30" t="s">
-        <v>225</v>
-      </c>
-      <c r="D49" s="31">
-        <v>4</v>
-      </c>
-      <c r="E49" s="32">
-        <v>4745.76</v>
-      </c>
-      <c r="F49" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G49" s="19" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="27" t="s">
-        <v>59</v>
-      </c>
-      <c r="B50" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C50" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="D50" s="30">
-        <v>2</v>
-      </c>
-      <c r="E50" s="33">
-        <v>1898.31</v>
-      </c>
-      <c r="F50" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G50" s="19" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="27" t="s">
-        <v>235</v>
-      </c>
-      <c r="B51" s="19" t="s">
-        <v>237</v>
-      </c>
-      <c r="C51" s="30" t="s">
-        <v>394</v>
-      </c>
-      <c r="D51" s="30">
-        <v>2</v>
-      </c>
-      <c r="E51" s="33">
-        <v>2372.88</v>
-      </c>
-      <c r="F51" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G51" s="19" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="B52" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="C52" s="30" t="s">
-        <v>378</v>
-      </c>
-      <c r="D52" s="30">
-        <v>2</v>
-      </c>
-      <c r="E52" s="33">
-        <v>2372.88</v>
-      </c>
-      <c r="F52" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G52" s="19" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="B53" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C53" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="D53" s="30">
-        <v>4</v>
-      </c>
-      <c r="E53" s="33">
-        <v>4745.76</v>
-      </c>
-      <c r="F53" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G53" s="19" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="27" t="s">
-        <v>387</v>
-      </c>
-      <c r="B54" s="19" t="s">
-        <v>388</v>
-      </c>
-      <c r="C54" s="30" t="s">
-        <v>389</v>
-      </c>
-      <c r="D54" s="30">
-        <v>2</v>
-      </c>
-      <c r="E54" s="33">
-        <v>13050.85</v>
-      </c>
-      <c r="F54" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G54" s="19" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="27" t="s">
-        <v>395</v>
-      </c>
-      <c r="B55" s="19" t="s">
-        <v>396</v>
-      </c>
-      <c r="C55" s="30" t="s">
+      <c r="E59" s="33">
+        <v>23305.08</v>
+      </c>
+      <c r="F59" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="G59" s="16" t="s">
         <v>397</v>
-      </c>
-      <c r="D55" s="30">
-        <v>2</v>
-      </c>
-      <c r="E55" s="33">
-        <v>4745.76</v>
-      </c>
-      <c r="F55" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G55" s="19" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="27" t="s">
-        <v>200</v>
-      </c>
-      <c r="B56" s="19" t="s">
-        <v>202</v>
-      </c>
-      <c r="C56" s="30" t="s">
-        <v>201</v>
-      </c>
-      <c r="D56" s="30">
-        <v>2</v>
-      </c>
-      <c r="E56" s="33">
-        <v>4745.76</v>
-      </c>
-      <c r="F56" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G56" s="19" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="B57" s="34" t="s">
-        <v>106</v>
-      </c>
-      <c r="C57" s="30" t="s">
-        <v>105</v>
-      </c>
-      <c r="D57" s="30">
-        <v>2</v>
-      </c>
-      <c r="E57" s="33">
-        <v>5932.2</v>
-      </c>
-      <c r="F57" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G57" s="19" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="B58" s="34" t="s">
-        <v>52</v>
-      </c>
-      <c r="C58" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="D58" s="30">
-        <v>2</v>
-      </c>
-      <c r="E58" s="33">
-        <v>6525.42</v>
-      </c>
-      <c r="F58" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G58" s="19" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="35" t="s">
-        <v>384</v>
-      </c>
-      <c r="B59" s="34" t="s">
-        <v>385</v>
-      </c>
-      <c r="C59" s="37" t="s">
-        <v>400</v>
-      </c>
-      <c r="D59" s="35">
-        <v>2</v>
-      </c>
-      <c r="E59" s="36">
-        <v>23305.08</v>
-      </c>
-      <c r="F59" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="G59" s="19" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
